--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosagebase.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationdosagebase.xlsx
@@ -259,7 +259,7 @@
     <t>薬の服用方法・服用した方法、または服用すべき方法</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -321,7 +321,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -875,7 +875,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
@@ -930,7 +930,7 @@
     <t>期間にわたって被験者に投与される可能性のある治療物質の最大総量。たとえば、24時間で1000mg。 / The maximum total quantity of a therapeutic substance that may be administered to a subject over the period of time.  For example, 1000mg in 24 hours.</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.empty() xor denominator.exists()) and (numerator.exists() or extension.exists())}</t>
   </si>
   <si>
